--- a/docs/02_基本設計/07_非機能/KF-BD-010_非機能設計書.xlsx
+++ b/docs/02_基本設計/07_非機能/KF-BD-010_非機能設計書.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,11 +91,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +148,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -492,6 +526,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -500,6 +537,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -511,7 +550,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -524,7 +563,7 @@
           <t>KF-BD-010</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -534,10 +573,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -550,7 +589,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -563,8 +602,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -611,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -670,6 +711,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §4/§5 とログイン堅牢化の実装に合わせて更新：JWT 有効 2 時間、パスワード 12 文字以上、アカウントロック、PostgreSQL＋Flyway、Docker Compose、環境変数管理を反映。環境分離・CI・監視・復旧目標を追加。未実装事項（失効・監査ログ・手動解除・サーバー側強制）を明記</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -683,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -793,12 +857,12 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>JWT。有効期限8時間</t>
+          <t>JWT（HS256）。有効期限 2 時間</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>リフレッシュは将来</t>
+          <t>リフレッシュ方式・サーバー側失効（ログアウトの無効化）は未実装（KF-RD-002 §4。今後の課題）</t>
         </is>
       </c>
     </row>
@@ -815,12 +879,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>BCryptでハッシュ化。8文字以上</t>
+          <t>BCrypt でハッシュ化。12 文字以上・英字と数字を両方含む・現在のパスワードと異なる（ONL-023 / API-023）</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>平文保存禁止</t>
+          <t>平文保存禁止。上限は BCrypt の入力上限に合わせ 72 文字（@Size）。記号の要否・過去パスワードの再利用禁止・有効期限は規定しない</t>
         </is>
       </c>
     </row>
@@ -859,12 +923,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>本番想定はHTTPS</t>
+          <t>本番は HTTPS（リバースプロキシで終端）。CORS は許可オリジンを設定で指定</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>開発はHTTP</t>
+          <t>開発は HTTP。nginx で X-Content-Type-Options: nosniff／X-Frame-Options: DENY／Referrer-Policy: no-referrer を付与。CSP は今後の課題（KF-RD-002 §4）</t>
         </is>
       </c>
     </row>
@@ -925,7 +989,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>毎日1回、7世代</t>
+          <t>毎日 1 回、7 世代。本番はマネージド PostgreSQL の自動日次バックアップ＋暗号化保管、復元訓練は四半期ごと（KF-RD-002 §4）</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -972,7 +1036,11 @@
           <t>承認操作は approval_steps に操作者・日時を記録</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ログイン成否を含む監査ログ（audit_logs）は未実装（KF-RD-002 §4。今後の課題）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1009,12 +1077,12 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>開発はH2、本番想定はPostgreSQL。SQLは共通機能の範囲で記述</t>
+          <t>開発・本番とも PostgreSQL。DB の変更は Flyway（V&lt;番号&gt;__&lt;内容&gt;.sql）で版管理し、アプリは ddl-auto=validate で起動時に検証する</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Flyway等は将来</t>
+          <t>V1__init_schema.sql は変更しない（変更は新しい版で追加）。開発 DB の作り直しは backend/db/reset-dev.sql。詳細は KF-DD-006</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1121,166 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>開発はローカル起動。Docker化は将来</t>
+          <t>Docker Compose で postgres（18）／backend／frontend（nginx）の 3 コンテナを起動（docker compose up -d --build）。ヘルスチェックは actuator の health のみ公開</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>README に手順を記載</t>
+          <t>設定・秘密情報は環境変数（.env。Git 管理外）で注入し、.env.example を雛形にする。JWT 鍵・DB パスワードをソースに置かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>アカウントロック</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ログイン失敗 5 回で 30 分ロック（locked_until）。ロック中は正しいパスワードでも E-017（HTTP 423）。成功で失敗回数とロックを解除</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>管理者による手動解除は未実装（30 分で自動解除）。ロック中の試行は失敗回数に加算しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>認証エラー応答</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>401（E-001）・403（E-010）を JSON で返す（AuthenticationEntryPoint / AccessDeniedHandler）</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>失敗原因（不存在・無効・不一致）は同一メッセージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワード</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワードの利用者（must_change_password=true）は SCR-007 で変更するまで他画面へ入れない</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>サーバー側の強制は未実装（画面のルーターガードのみ）。既知の課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>環境分離</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>開発／検証／本番の 3 環境で設定を分離し、本番データを開発に持ち込まない。環境ごとに .env（または環境変数）を用意</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §5。現状は開発環境のみ構築済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>GitHub Actions（.github/workflows/ci.yml）で push 時にビルド・テストを自動実行</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>脆弱性検査・検証環境への自動配置・本番の承認付き配置は今後の課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>構造化ログ（JSON）、エラー率・応答時間・バッチ成否の監視と通知、バッチ失敗時の管理者通知</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §5。未実装（現状は actuator health のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>可用性</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>復旧目標</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>復旧時間 4 時間以内、データ損失 1 日以内（バックアップ周期）</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §5</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/07_非機能/KF-BD-010_非機能設計書.xlsx
+++ b/docs/02_基本設計/07_非機能/KF-BD-010_非機能設計書.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -124,11 +124,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +155,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,7 +582,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -652,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -734,6 +743,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装との照合。認証（JWT 2 時間・トークン無効化・強制パスワード変更のサーバー側実装・アカウントロック・パスワードポリシー）、時刻（Asia/Tokyo）、保存期間（物理削除なし）、CSV 数式インジェクション対策を実装に合わせて更新。実装状況列を追加し、定期バッチ（BAT-001〜003）・月次締め・36協定アラート・打刻修正申請の期限（翌月3営業日）・メール通知を「未実装（今後）」として明記</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>管理者によるパスワード設定にも本人変更と同じポリシー（12〜72 文字・英字と数字）を適用、管理者によるパスワード再設定で password_changed_at を更新して旧トークンを失効させる点を実装に合わせて修正。開発用シードの起動条件（kintaiflow.dev.seed-enabled=true）、Flyway V3〜V5（2028 年祝日・休憩離席・休憩離席修正）を追記。未実装事項に休憩不足の警告、休憩・離席の取消・削除、監査ログ・退職処理、代理承認・プロジェクト／現場、ログアウト時のトークン失効・休暇付与の削除／一括付与、W-001 確認ダイアログ・401 時の画面メッセージを追加</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -747,34 +802,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>設計方針</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>備考</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>実装状況</t>
         </is>
       </c>
     </row>
@@ -796,7 +857,12 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>300名規模で想定</t>
+          <t>300名規模で想定。月次集計は 1 本の集計 SQL（GROUP BY）で取得</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>未検証</t>
         </is>
       </c>
     </row>
@@ -818,7 +884,12 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>月末・月初に集中</t>
+          <t>月末・月初に集中。負荷試験は未実施</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>未検証</t>
         </is>
       </c>
     </row>
@@ -843,6 +914,11 @@
           <t>学習用途のため24h要件なし</t>
         </is>
       </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>未照合</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -857,12 +933,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>JWT（HS256）。有効期限 2 時間</t>
+          <t>JWT（HS256）。有効期限 2 時間（kintaiflow.jwt.expiration-hours）。署名鍵は設定値（Git 管理外）</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>リフレッシュ方式・サーバー側失効（ログアウトの無効化）は未実装（KF-RD-002 §4。今後の課題）</t>
+          <t>ログイン時にメールアドレスを前後空白除去・小文字化して照合。リフレッシュ方式・ログアウトによるサーバー側失効は未実装（KF-RD-002 §4。今後の課題）</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
@@ -874,17 +955,22 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>パスワード</t>
+          <t>トークンの無効化</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>BCrypt でハッシュ化。12 文字以上・英字と数字を両方含む・現在のパスワードと異なる（ONL-023 / API-023）</t>
+          <t>リクエストごとに users を検索し、ユーザーが無効化（INACTIVE）・削除されていたら 401（E-001）。パスワード変更・管理者による再設定の前に発行されたトークンも 401（ActiveUserFilter）</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>平文保存禁止。上限は BCrypt の入力上限に合わせ 72 文字（@Size）。記号の要否・過去パスワードの再利用禁止・有効期限は規定しない</t>
+          <t>管理者によるパスワード再設定でも password_changed_at を更新するため、再設定前に発行されたトークンは 401（E-001）になる（再ログインが必要）。ロール変更は既発行トークンの role には反映されない（最長 2 時間）</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
@@ -896,17 +982,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>認可</t>
+          <t>パスワード</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>API毎にロールとデータ所有を検証</t>
+          <t>BCrypt でハッシュ化。変更時は 12 文字以上・半角の英字と数字を両方含む・現在のパスワードと異なる・UTF-8 で 72 バイト以内（ONL-023 / API-023）</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>画面制御に依存しない</t>
+          <t>平文保存禁止。記号の要否・過去パスワードの再利用禁止・有効期限は規定しない。管理者が設定する初期・再設定パスワードにも同じポリシー（12〜72 文字・半角英字と数字を両方含む）を適用し（UserService#checkPolicy。違反は E-002）、設定後は本人が変更するまで他の API を使えない</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
@@ -918,17 +1009,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>認可</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>本番は HTTPS（リバースプロキシで終端）。CORS は許可オリジンを設定で指定</t>
+          <t>SecurityConfig（/api/admin/** は ADMIN）＋ Controller の @PreAuthorize ＋ Service のデータ所有検証の多重防御。承認系は DB でロール・ACTIVE を再確認</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>開発は HTTP。nginx で X-Content-Type-Options: nosniff／X-Frame-Options: DENY／Referrer-Policy: no-referrer を付与。CSP は今後の課題（KF-RD-002 §4）</t>
+          <t>画面制御に依存しない。詳細は KF-BD-004</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
@@ -940,281 +1036,346 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>入力値</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Bean Validationで検証。SQLはJPAのパラメータバインドのみ</t>
+          <t>本番は HTTPS（リバースプロキシで終端）。CORS は許可オリジンを設定で指定（許可メソッド GET/POST/PUT/DELETE/OPTIONS、ヘッダー Authorization / Content-Type）。CSRF は無効（トークン方式・セッションなし）</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>SQLインジェクション・XSS対策</t>
+          <t>開発は HTTP。nginx で X-Content-Type-Options: nosniff／X-Frame-Options: DENY／Referrer-Policy: no-referrer を付与。CSP は今後の課題（KF-RD-002 §4）。nginx・HTTPS 設定はインフラ構成側で、本照合の対象外</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>未照合</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>セキュリティ</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>保存期間</t>
+          <t>入力値</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>勤怠・申請データは5年以上保持（労基法109条・当面の運用）</t>
+          <t>Bean Validation で検証。SQLはJPAのパラメータバインドのみ（native SQL もパラメータ化）</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>物理削除しない</t>
+          <t>SQLインジェクション・XSS対策。CSV 出力は先頭が = + - @ タブ CR のセルに ' を付けて数式インジェクションを防ぐ</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>セキュリティ</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>バックアップ</t>
+          <t>アカウントロック</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>毎日 1 回、7 世代。本番はマネージド PostgreSQL の自動日次バックアップ＋暗号化保管、復元訓練は四半期ごと（KF-RD-002 §4）</t>
+          <t>ログイン失敗 5 回で 30 分ロック（locked_until）。ロック中は正しいパスワードでも E-017（HTTP 423）。成功で失敗回数とロックを解除。パスワード変更での現在のパスワード誤りも失敗回数に加算</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>BAT-003</t>
+          <t>ロック中の試行は失敗回数に加算しない。専用の手動解除機能は未実装（30 分で自動解除。管理者のパスワード再設定でも解除される）</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>ログ</t>
+          <t>セキュリティ</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>アプリログ</t>
+          <t>認証エラー応答</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>INFO以上をファイル出力。個人情報はマスク</t>
+          <t>401（E-001）・403（E-010）を JSON で返す（AuthenticationEntryPoint / AccessDeniedHandler）</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>logback</t>
+          <t>失敗原因（不存在・無効・不一致）は同一メッセージ</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ログ</t>
+          <t>セキュリティ</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>監査</t>
+          <t>初期パスワード（強制変更）</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>承認操作は approval_steps に操作者・日時を記録</t>
+          <t>初期パスワード・管理者再設定直後の利用者（must_change_password=true）は、本人が変更するまで /api/auth/password 以外の API が 403（E-019）。画面はルーターガードで SCR-007 へ誘導し、左メニューは変更が済むまで無効表示にする</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>ログイン成否を含む監査ログ（audit_logs）は未実装（KF-RD-002 §4。今後の課題）</t>
+          <t>サーバー側で強制（PasswordChangeRequiredFilter。トークンの mcp クレーム）。パスワード変更後は旧トークンが無効になるため再ログインが必要</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>保守性</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>構成</t>
+          <t>保存期間</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Controller / Service / Repository の3層</t>
+          <t>勤怠・申請データは5年以上保持（労基法109条・当面の運用）</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>KF-DD-005</t>
+          <t>アプリは勤怠・申請・承認履歴を物理削除しない（削除できるのは祝日マスタのみ）。保存期間経過後のアーカイブ・削除処理は未実装</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>保守性</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>時刻の扱い</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>開発・本番とも PostgreSQL。DB の変更は Flyway（V&lt;番号&gt;__&lt;内容&gt;.sql）で版管理し、アプリは ddl-auto=validate で起動時に検証する</t>
+          <t>業務時刻は Asia/Tokyo。Clock Bean で取得し、DB 接続も SET TIME ZONE 'Asia/Tokyo'。TIMESTAMP は JST の無印日時で保存、API では +09:00 付き ISO 8601 で返す</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>V1__init_schema.sql は変更しない（変更は新しい版で追加）。開発 DB の作り直しは backend/db/reset-dev.sql。詳細は KF-DD-006</t>
+          <t>サーバーが UTC でも JST で動作する（Clock.system(Asia/Tokyo)）</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>互換性</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>ブラウザ</t>
+          <t>バックアップ</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Chrome / Edge 最新版</t>
+          <t>毎日 1 回、7 世代。本番はマネージド PostgreSQL の自動日次バックアップ＋暗号化保管、復元訓練は四半期ごと（KF-RD-002 §4）</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Vue 3 SPA</t>
+          <t>BAT-003。アプリケーション（backend/）にバックアップ処理は無い（インフラ側の運用）</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>ログ</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>起動</t>
+          <t>アプリログ</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Docker Compose で postgres（18）／backend／frontend（nginx）の 3 コンテナを起動（docker compose up -d --build）。ヘルスチェックは actuator の health のみ公開</t>
+          <t>INFO以上を出力（SLF4J）。氏名・メール・理由・パスワード・トークンはログに出さず、ID・件数のみを出す</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>設定・秘密情報は環境変数（.env。Git 管理外）で注入し、.env.example を雛形にする。JWT 鍵・DB パスワードをソースに置かない</t>
+          <t>現行は標準出力のみ（logback 設定ファイルなし）。ファイル出力・ローテーションは今後の課題</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>セキュリティ</t>
+          <t>ログ</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>アカウントロック</t>
+          <t>監査</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>ログイン失敗 5 回で 30 分ロック（locked_until）。ロック中は正しいパスワードでも E-017（HTTP 423）。成功で失敗回数とロックを解除</t>
+          <t>承認操作は approval_steps に操作者・日時・コメントを記録。承認・付与などの操作は INFO ログに操作者 ID を出力</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>管理者による手動解除は未実装（30 分で自動解除）。ロック中の試行は失敗回数に加算しない</t>
+          <t>ログイン成否を含む監査ログ（audit_logs）は未実装（KF-RD-002 §4。今後の課題）</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>セキュリティ</t>
+          <t>保守性</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>認証エラー応答</t>
+          <t>構成</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>401（E-001）・403（E-010）を JSON で返す（AuthenticationEntryPoint / AccessDeniedHandler）</t>
+          <t>Controller / Service / Repository の3層</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>失敗原因（不存在・無効・不一致）は同一メッセージ</t>
+          <t>KF-DD-005</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>セキュリティ</t>
+          <t>保守性</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>初期パスワード</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>初期パスワードの利用者（must_change_password=true）は SCR-007 で変更するまで他画面へ入れない</t>
+          <t>開発・本番とも PostgreSQL。DB の変更は Flyway（V&lt;番号&gt;__&lt;内容&gt;.sql）で版管理し、アプリは ddl-auto=validate で起動時に検証する</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>サーバー側の強制は未実装（画面のルーターガードのみ）。既知の課題</t>
+          <t>V1__init_schema.sql は変更しない（変更は新しい版で追加）。V2__seed_holidays.sql で 2026〜2027 年、V3 で 2028 年（推算値。内閣府の公表値との照合は未実施）の祝日・年末年始を投入。V4 で attendance_breaks（休憩・離席）、V5 で requests に休憩・離席修正の列を追加（現在の最新は V5、次は V6）。開発 DB の作り直しは backend/db/reset-dev.sql。詳細は KF-DD-006</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>互換性</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>環境分離</t>
+          <t>ブラウザ</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>開発／検証／本番の 3 環境で設定を分離し、本番データを開発に持ち込まない。環境ごとに .env（または環境変数）を用意</t>
+          <t>Chrome / Edge 最新版</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>KF-RD-002 §5。現状は開発環境のみ構築済み</t>
+          <t>Vue 3 SPA（画面は 900px 以下でメニューを折りたたむ）</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
@@ -1226,17 +1387,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>起動</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>GitHub Actions（.github/workflows/ci.yml）で push 時にビルド・テストを自動実行</t>
+          <t>Docker Compose で postgres（18）／backend／frontend（nginx）の 3 コンテナを起動（docker compose up -d --build）。ヘルスチェックは actuator の health のみ公開</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>脆弱性検査・検証環境への自動配置・本番の承認付き配置は今後の課題</t>
+          <t>設定・秘密情報は環境変数（.env。Git 管理外）で注入し、.env.example を雛形にする。JWT 鍵・DB パスワードをソースに置かない。開発用の 100 名と休暇付与のシード（DevDataInitializer・DevLeaveBalanceInitializer）は、kintaiflow.dev.seed-password に加えて kintaiflow.dev.seed-enabled=true のときだけ動く（application-local.properties で設定。本番では未設定にする）。初期管理者は BOOTSTRAP_ADMIN_* で作成（パスワードがポリシー違反なら起動失敗）</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
@@ -1248,39 +1414,373 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>監視</t>
+          <t>環境分離</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>構造化ログ（JSON）、エラー率・応答時間・バッチ成否の監視と通知、バッチ失敗時の管理者通知</t>
+          <t>開発／検証／本番の 3 環境で設定を分離し、本番データを開発に持ち込まない。環境ごとに .env（または環境変数）を用意</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>KF-RD-002 §5。未実装（現状は actuator health のみ）</t>
+          <t>KF-RD-002 §5。現状は開発環境のみ構築済み</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>一部実装</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>GitHub Actions（.github/workflows/ci.yml）で push 時にビルド・テストを自動実行</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>脆弱性検査・検証環境への自動配置・本番の承認付き配置は今後の課題</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>未照合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>構造化ログ（JSON）、エラー率・応答時間・バッチ成否の監視と通知、バッチ失敗時の管理者通知</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §5。未実装（現状は actuator health のみ）</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>可用性</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>復旧目標</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>復旧時間 4 時間以内、データ損失 1 日以内（バックアップ周期）</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>KF-RD-002 §5</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>未照合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>定期バッチ</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>年次有給休暇の自動付与（BAT-001）、年5日取得義務アラート（BAT-002）、データバックアップ（BAT-003）</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>アプリケーション（backend/）に @Scheduled 等の定期処理は無い。年休の付与は管理者の手動付与（API-017）のみ。BAT-002 用の抽出メソッド（findAlertBaseRows）と通知種別 LEAVE_ALERT は用意済み</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>月次締め</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>月次締め（締め後の打刻・申請の変更禁止）</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>未実装。過去月の打刻修正申請・休暇申請も可能で、月次集計は常に最新データで再計算する</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>36協定アラート</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>月 45 時間超などの時間外上限アラート</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>未実装（通知・メールは発行しない）。部下の集計画面（SCR-203）で月間残業が 45 時間を超える行を赤字表示するのみ</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>打刻修正申請の期限</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>打刻修正申請は翌月 3 営業日までとする運用ルール</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>未実装。対象日が本日以前であれば期限なく申請できる（E-003 は未来日のみ）</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>メール通知</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>申請・承認時のメール通知（IF-003）</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>未実装。通知は画面内通知のみ（notifications テーブル）</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>休憩不足の警告</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>休憩が法定（6 時間超 45 分・8 時間超 60 分）に満たない場合の警告</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>未実装。休憩を 1 回でも打刻した日は打刻合計だけを控除する（不足していても法定休憩は補わない）。休憩・離席の打刻の取消・削除、0 分の区間の自動破棄も未実装（修正は休憩・離席修正申請）</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>監査ログ・退職処理</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>操作履歴の監査ログ（audit_logs）、退職者の処理</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>未実装。ユーザーは無効化（INACTIVE）のみ。承認操作は approval_steps に記録</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>代理承認・プロジェクト／現場</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>承認者不在時の代理承認、プロジェクト・現場別の工数管理</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>未実装</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>ログアウト時のトークン失効・休暇付与の削除／一括付与</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>ログアウト操作によるサーバー側トークン失効、休暇付与行の削除・一括付与</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>未実装。トークンは期限（2 時間）またはパスワード変更・再設定まで有効。付与は 1 件ずつの追加と日数調整のみ</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>機能（未実装）</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>提出時の確認ダイアログ・401 時の画面メッセージ</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>申請提出前の確認（W-001）、認証切れ（401）時にログイン画面へ戻す際のメッセージ表示</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>未実装。提出は確認なしで即実行。401 ではトークンを破棄してログイン画面へ戻るのみ</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
         </is>
       </c>
     </row>
